--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/CSTPSelect001_R.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/CSTPSelect001_R.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>交易类型</t>
   </si>
@@ -80,6 +80,10 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>业务编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -432,13 +436,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="19" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -502,7 +506,10 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" t="s">
         <v>21</v>
       </c>
     </row>
